--- a/artfynd/A 40568-2022 artfynd.xlsx
+++ b/artfynd/A 40568-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65589808</v>
       </c>
       <c r="B2" t="n">
-        <v>57484</v>
+        <v>57487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2022 artfynd.xlsx
+++ b/artfynd/A 40568-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>65589808</v>
       </c>
       <c r="B2" t="n">
-        <v>57487</v>
+        <v>57488</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 40568-2022 artfynd.xlsx
+++ b/artfynd/A 40568-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>65589808</v>
+        <v>59454980</v>
       </c>
       <c r="B2" t="n">
         <v>57488</v>
@@ -708,11 +708,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
@@ -756,12 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-05-15</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-05-15</t>
+          <t>2016-05-09</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 40568-2022 artfynd.xlsx
+++ b/artfynd/A 40568-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>59454980</v>
+        <v>65589808</v>
       </c>
       <c r="B2" t="n">
         <v>57488</v>
@@ -708,7 +708,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
@@ -752,12 +756,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-05-09</t>
+          <t>2017-05-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-05-09</t>
+          <t>2017-05-15</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 40568-2022 artfynd.xlsx
+++ b/artfynd/A 40568-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>65589808</v>
+        <v>56945300</v>
       </c>
       <c r="B2" t="n">
-        <v>57510</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102119</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Härlöv N, Härlöv, Sm</t>
+          <t>Härlöv Alvesta, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478570</v>
+        <v>478658</v>
       </c>
       <c r="R2" t="n">
-        <v>6314770</v>
+        <v>6314796</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-05-15</t>
+          <t>2013-08-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-05-15</t>
+          <t>2013-08-27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,19 +756,897 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>vid skogskant # asp</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Annchristin Nyström</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Annchristin Nyström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>59454980</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57942</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102119</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Göktyta</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Jynx torquilla</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Härlöv N, Härlöv, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>478570</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6314770</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Härlöv</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2016-05-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2016-05-09</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Martin Unell</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Martin Unell</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>77170836</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57546</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102963</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skrattmås</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chroicocephalus ridibundus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Syd om Lövåsen, Härlöv, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>478750</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6314823</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Härlöv</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>77170832</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Syd om Lövåsen, Härlöv, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>478750</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6314823</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Härlöv</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>77170824</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Syd om Lövåsen, Härlöv, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>478750</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6314823</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Härlöv</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>77170829</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Syd om Lövåsen, Härlöv, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>478750</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6314823</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Härlöv</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>77170816</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Syd om Lövåsen, Härlöv, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>478750</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6314823</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Härlöv</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>92556784</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Syd om Lövåsen, Härlöv, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>478750</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6314823</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Härlöv</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-04-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-04-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>77170830</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Syd om Lövåsen, Härlöv, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>478750</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6314823</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Härlöv</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Hugo Johansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40568-2022 artfynd.xlsx
+++ b/artfynd/A 40568-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56945300</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134982478</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59454980</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77170836</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1215,6 +1240,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77170832</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77170824</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1433,6 +1468,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77170829</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1542,6 +1582,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77170816</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1647,6 +1692,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92556784</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1756,8 +1806,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77170830</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 40568-2022 artfynd.xlsx
+++ b/artfynd/A 40568-2022 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>134982478</v>
       </c>
       <c r="B3" t="n">
-        <v>57912</v>
+        <v>57917</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
